--- a/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_pl.xlsx
+++ b/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_pl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akazmierczak\Documents\Quantum Qguar\Qcadoo\Szablony\Import do Qcadoo\propozycje\PL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBEFD9E-9B24-48A2-85B5-37C1B674505B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B40C71-2A12-7D41-9B01-F099E35E7CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produkty - import" sheetId="1" r:id="rId1"/>
@@ -504,7 +504,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Numer</t>
   </si>
@@ -582,13 +582,16 @@
   </si>
   <si>
     <t>finalny produkt</t>
+  </si>
+  <si>
+    <t>Ewidencja daty ważności</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -640,6 +643,12 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -661,11 +670,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1385,9 +1395,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="productImportSchema_pl" displayName="productImportSchema_pl" ref="A1:R2" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:R2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="productImportSchema_pl" displayName="productImportSchema_pl" ref="A1:S2" insertRow="1" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:S2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Numer" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nazwa" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Globalny typ materiału"/>
@@ -1406,6 +1416,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Rozmiar"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Ważność"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Ewidencja partii"/>
+    <tableColumn id="19" xr3:uid="{F73D373E-3DAF-DC42-B43C-8ACD83ECED1A}" name="Ewidencja daty ważności"/>
   </tableColumns>
   <tableStyleInfo name="Styl tabeli 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1432,9 +1443,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1472,7 +1483,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1578,7 +1589,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1720,7 +1731,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1731,22 +1742,23 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="16.875" customWidth="1"/>
+    <col min="1" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="22.625" customWidth="1"/>
-    <col min="5" max="5" width="21.375" customWidth="1"/>
-    <col min="6" max="11" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="11" width="16.83203125" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="20.875" customWidth="1"/>
-    <col min="16" max="18" width="16.875" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="18" width="16.83203125" customWidth="1"/>
+    <col min="19" max="19" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1801,8 +1813,11 @@
       <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="D2" s="2"/>
@@ -1842,12 +1857,12 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1855,7 +1870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1863,7 +1878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1871,17 +1886,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
